--- a/Clasificacion.xlsx
+++ b/Clasificacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariana Vallejos\Documents\Femócratas Lucía Miranda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15B52CF-9769-476B-B91F-9258A7C70BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79240E8-81F0-BD46-B1F2-E227AB529A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="51">
   <si>
     <t>Entrevistas</t>
   </si>
@@ -128,13 +128,58 @@
   </si>
   <si>
     <t>Entrevista 20</t>
+  </si>
+  <si>
+    <t>AUTONOMA</t>
+  </si>
+  <si>
+    <t>ESTADO-PUNTO FOCAL</t>
+  </si>
+  <si>
+    <t>NACIONAL</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>MOVIMENTISTA</t>
+  </si>
+  <si>
+    <t>PROFESIONAL</t>
+  </si>
+  <si>
+    <t>ESTADO-PROFESIONAL</t>
+  </si>
+  <si>
+    <t>PROVINCIAL</t>
+  </si>
+  <si>
+    <t>MILITANTE</t>
+  </si>
+  <si>
+    <t>GOBIERNO</t>
+  </si>
+  <si>
+    <t>MOVIMIENTISTA</t>
+  </si>
+  <si>
+    <t>MOVIMENTISTA-MILITANTE</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>España</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -156,6 +201,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -190,15 +249,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,370 +483,652 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="41.4">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.8">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:6" ht="15">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.8">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:6" ht="15">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:6" ht="30">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.8">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:6" ht="15">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.8">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:6" ht="15">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.8">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.6">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:6" ht="30">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="13.8">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.6">
+    <row r="10" spans="1:6" ht="30">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="27.6">
+    <row r="11" spans="1:6" ht="30">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27.6">
+    <row r="12" spans="1:6" ht="30">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.8">
+    <row r="13" spans="1:6" ht="15">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.8">
+    <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.6">
+    <row r="15" spans="1:6" ht="30">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.8">
+    <row r="16" spans="1:6" ht="15">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="13.8">
+    <row r="17" spans="1:6" ht="15">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="13.8">
+    <row r="18" spans="1:6" ht="15">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="13.8">
+    <row r="19" spans="1:6" ht="15">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="13.8">
+    <row r="20" spans="1:6" ht="15">
       <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="13.8">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="13.2">
-      <c r="A22" s="4"/>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>